--- a/docs/data/jp/xlsx/5532.xlsx
+++ b/docs/data/jp/xlsx/5532.xlsx
@@ -7241,7 +7241,7 @@
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Loss Compensation Ope CF</t>
+          <t>손해보상손실 충당금 증감액</t>
         </is>
       </c>
       <c r="C115" s="22" t="n">
@@ -7278,7 +7278,7 @@
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>Gain On Donation Of Noncurrent Assets Ope CF</t>
+          <t>고정자산 수증이익</t>
         </is>
       </c>
       <c r="C116" s="22" t="n">
@@ -7716,7 +7716,7 @@
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Contract Asset Ope CF</t>
+          <t>계약자산 증감액</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
@@ -7753,7 +7753,7 @@
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Costs On Construction Contracts In Progress Ope CF</t>
+          <t>미성공사 지출금 증감액</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
@@ -7790,7 +7790,7 @@
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Costs On Uncompleted Services Ope CF</t>
+          <t>미성업무 지출금 증감액</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
@@ -7827,7 +7827,7 @@
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Real Estate For Sale Ope CF</t>
+          <t>판매용 부동산 증감액</t>
         </is>
       </c>
       <c r="C134" s="22" t="n">
@@ -8217,7 +8217,7 @@
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Guarantee Deposits Received Ope CF</t>
+          <t>예수보증금 증감액</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
@@ -8532,7 +8532,7 @@
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>Compensation Paid Ope CF</t>
+          <t>보상금 지급액</t>
         </is>
       </c>
       <c r="C155" s="22" t="n">
@@ -8557,7 +8557,7 @@
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>Support Money Received Ope CF</t>
+          <t>협찬금 수취액</t>
         </is>
       </c>
       <c r="C156" s="22" t="n">
@@ -8594,7 +8594,7 @@
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>Penalty Paid Ope CF</t>
+          <t>위약금 지급액</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
@@ -8986,7 +8986,7 @@
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Other Investments Inv CF</t>
+          <t>투자 및 기타자산 증감액</t>
         </is>
       </c>
       <c r="C171" s="22" t="n">
@@ -9255,7 +9255,7 @@
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>Payments For Issuance Of Common Stock Fin CF</t>
+          <t>주식 발행 지출</t>
         </is>
       </c>
       <c r="C179" s="22" t="n">
@@ -9289,7 +9289,7 @@
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>Deposit For Subscriptions To Shares Income Fin CF</t>
+          <t>신주청약증거금 납입 수입</t>
         </is>
       </c>
       <c r="E180" s="22" t="n">
@@ -9426,7 +9426,7 @@
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>Commission Fee Paid Fin CF</t>
+          <t>수수료 지급액</t>
         </is>
       </c>
       <c r="C185" s="22" t="n">
@@ -9463,7 +9463,7 @@
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>Payment Of Listing Expenses Fin CF</t>
+          <t>상장 관련 비용 지출</t>
         </is>
       </c>
       <c r="E186" s="22" t="n">
@@ -12090,7 +12090,7 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Operating Accounts Receivable CA</t>
+          <t>영업미수금</t>
         </is>
       </c>
       <c r="C72" s="22" t="n">
@@ -12260,7 +12260,7 @@
     <row r="77">
       <c r="A77" s="20" t="inlineStr">
         <is>
-          <t>Costs On Uncompleted Services</t>
+          <t>미성업무 지출금</t>
         </is>
       </c>
       <c r="H77" s="22" t="n">
@@ -12650,7 +12650,7 @@
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>Accumulated Depreciation And Impairment Loss PPEBy Group</t>
+          <t>감가상각누계액 및 손상차손누계액</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
@@ -13086,7 +13086,7 @@
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>Operating Accounts Payable</t>
+          <t>영업미지급금</t>
         </is>
       </c>
       <c r="C102" s="22" t="n">
@@ -13467,7 +13467,7 @@
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>Provision For Loss Compensation CL</t>
+          <t>손해보상손실 충당금</t>
         </is>
       </c>
       <c r="D114" s="22" t="n">
@@ -13492,7 +13492,7 @@
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>Provision For Compensation CL</t>
+          <t>손해보상손실 충당금</t>
         </is>
       </c>
       <c r="C115" s="22" t="n">
@@ -13675,7 +13675,7 @@
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>Guarantee Deposits Received2NCL</t>
+          <t>예수보증금</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
@@ -13907,7 +13907,7 @@
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>Deposit For Subscriptions To Shares</t>
+          <t>신주청약증거금</t>
         </is>
       </c>
       <c r="J128" s="22" t="n">

--- a/docs/data/jp/xlsx/5532.xlsx
+++ b/docs/data/jp/xlsx/5532.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC188"/>
+  <dimension ref="A1:AC194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4169,10 +4172,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>3525</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4207,7 +4212,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>6487650</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5406,7 +5413,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5652,402 +5659,470 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>1591.928</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>2201.369</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>1847.602</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>1286.301</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>1320.913</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>2410.547</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>2861.804</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>1429.712</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>1412.849</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>2837.032</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>1414.472</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>1720.312</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>1591.928</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>1320.913</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>1412.849</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>165.244</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>387.013</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>577.8390000000001</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>171.337</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>156.112</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>406.085</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>707.425</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>344.776</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>218.8</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1114.254</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>307.506</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>315.807</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>165.244</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>156.112</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>218.8</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>107.555</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>126.462</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>135.414</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>126.925</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>136.726</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>168.756</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>162.153</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>147.934</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>155.063</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>201.594</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>176.52</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>198.919</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>107.555</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>136.726</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>155.063</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>57.689</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>260.55</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>442.426</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>44.411</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>19.386</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>237.328</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>545.273</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>196.842</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>63.736</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>912.659</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>130.987</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>116.887</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>57.689</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>19.386</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>63.736</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.005</v>
+        <v>107.555</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0</v>
+        <v>126.462</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0.08599999999999999</v>
+        <v>135.414</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.368</v>
+        <v>126.925</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.422</v>
+        <v>136.726</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0.304</v>
+        <v>168.756</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>1.19</v>
+        <v>162.153</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0.523</v>
+        <v>147.934</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>2.314</v>
+        <v>155.063</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0.403</v>
+        <v>201.594</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>1.854</v>
+        <v>176.52</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>0.407</v>
+        <v>198.919</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.005</v>
+        <v>107.555</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>0.422</v>
+        <v>136.726</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>2.314</v>
+        <v>155.063</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>57.689</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>260.55</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>442.426</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>44.411</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>19.386</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>237.328</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>545.273</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>196.842</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>63.736</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>912.659</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>130.987</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>116.887</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>57.689</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>19.386</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>63.736</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>협찬금 수입</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>0</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>0.208</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>0.237</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>0.04</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="D87" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>0.408</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>1.248</v>
+        <v>0.368</v>
       </c>
       <c r="G87" s="22" t="n">
         <v>0.422</v>
@@ -6056,417 +6131,402 @@
         <v>0.304</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>1.399</v>
+        <v>1.19</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>1.303</v>
+        <v>0.523</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>3.525</v>
+        <v>2.314</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>0.843</v>
+        <v>0.403</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>1.938</v>
+        <v>1.854</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>0.644</v>
+        <v>0.407</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="W87" s="22" t="n">
         <v>0.422</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>3.525</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>14.346</v>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>12.914</v>
-      </c>
-      <c r="E88" s="22" t="n">
-        <v>11.626</v>
+        <v>0</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>16.271</v>
+        <v>0</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>24.822</v>
-      </c>
-      <c r="H88" s="22" t="n">
-        <v>30.423</v>
-      </c>
-      <c r="I88" s="22" t="n">
-        <v>38.329</v>
-      </c>
-      <c r="J88" s="22" t="n">
-        <v>43.835</v>
-      </c>
-      <c r="K88" s="22" t="n">
-        <v>47.266</v>
-      </c>
-      <c r="L88" s="22" t="n">
-        <v>58.105</v>
-      </c>
-      <c r="M88" s="22" t="n">
-        <v>68.033</v>
-      </c>
-      <c r="N88" s="22" t="n">
-        <v>89.2</v>
+        <v>0</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>14.346</v>
+        <v>0</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>24.822</v>
-      </c>
-      <c r="X88" s="22" t="n">
-        <v>47.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>협찬금 수입</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="22" t="n">
-        <v>26.469</v>
-      </c>
       <c r="F89" s="22" t="n">
-        <v>28.878</v>
+        <v>0.88</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>16.035</v>
+        <v>0</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>0.446</v>
+        <v>0</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>0.036</v>
+        <v>0.209</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>35.816</v>
+        <v>0</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>12.739</v>
+        <v>0.21</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>23.735</v>
+        <v>0</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>2.555</v>
+        <v>0</v>
       </c>
       <c r="V89" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>35.816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>0.01</v>
       </c>
       <c r="D90" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>3.843</v>
+        <v>0.025</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>8.749000000000001</v>
+        <v>0</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>4.188</v>
+        <v>0</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>2.791</v>
+        <v>0</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>0.93</v>
+        <v>0.208</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>1.872</v>
+        <v>0.571</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>2.449</v>
+        <v>0.04</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>4.554</v>
+        <v>0.23</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>3.664</v>
+        <v>0.083</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>4.772</v>
+        <v>0.237</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>0.01</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>4.188</v>
+        <v>0</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>2.449</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>0.212</v>
+        <v>0.015</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>0.408</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0</v>
+        <v>1.248</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>0</v>
+        <v>0.422</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>3.525</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="N91" s="22" t="n">
+        <v>0.644</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>0.212</v>
+        <v>0.015</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>0</v>
+        <v>0.422</v>
+      </c>
+      <c r="X91" s="22" t="n">
+        <v>3.525</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>1.19</v>
+        <v>14.346</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>0.17</v>
+        <v>12.914</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>0.153</v>
+        <v>11.626</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>0.09</v>
+        <v>16.271</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>0.06</v>
+        <v>24.822</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>0</v>
+        <v>30.423</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>0</v>
+        <v>38.329</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>0</v>
+        <v>43.835</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>0</v>
+        <v>47.266</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>58.105</v>
+      </c>
+      <c r="M92" s="22" t="n">
+        <v>68.033</v>
+      </c>
+      <c r="N92" s="22" t="n">
+        <v>89.2</v>
       </c>
       <c r="V92" s="22" t="n">
-        <v>1.19</v>
+        <v>14.346</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>0.06</v>
+        <v>24.822</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>0</v>
+        <v>47.266</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>-0.111</v>
+        <v>0</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>0.094</v>
+        <v>26.469</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>0.396</v>
+        <v>28.878</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>1.665</v>
+        <v>16.035</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>0.777</v>
+        <v>0.446</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>0</v>
+        <v>35.816</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>0.371</v>
+        <v>12.739</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>0.416</v>
+        <v>23.735</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>1.063</v>
+        <v>2.555</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>-0.111</v>
+        <v>0</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>0</v>
+        <v>35.816</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
-        </is>
-      </c>
-      <c r="C94" s="22" t="n">
-        <v>15.815</v>
+          <t>감가상각비</t>
+        </is>
       </c>
       <c r="D94" s="22" t="n">
-        <v>13.254</v>
+        <v>0</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>42.187</v>
+        <v>3.843</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>54.383</v>
+        <v>8.749000000000001</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>29.092</v>
+        <v>4.188</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>50.915</v>
+        <v>2.791</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>40.482</v>
+        <v>0.93</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>45.743</v>
+        <v>1.872</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>85.53100000000001</v>
+        <v>2.449</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>75.77</v>
+        <v>4.554</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>95.849</v>
+        <v>3.664</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>121.531</v>
-      </c>
-      <c r="V94" s="22" t="n">
-        <v>15.815</v>
+        <v>4.772</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>29.092</v>
+        <v>4.188</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>85.53100000000001</v>
+        <v>2.449</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="n">
-        <v>41.889</v>
-      </c>
-      <c r="D95" s="12" t="n">
-        <v>247.296</v>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v>400.647</v>
-      </c>
-      <c r="F95" s="12" t="n">
-        <v>-8.725</v>
-      </c>
-      <c r="G95" s="12" t="n">
-        <v>-9.282999999999999</v>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>186.718</v>
-      </c>
-      <c r="I95" s="12" t="n">
-        <v>506.189</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>152.402</v>
-      </c>
-      <c r="K95" s="12" t="n">
-        <v>-18.27</v>
-      </c>
-      <c r="L95" s="12" t="n">
-        <v>837.732</v>
-      </c>
-      <c r="M95" s="12" t="n">
-        <v>37.077</v>
-      </c>
-      <c r="N95" s="12" t="n">
-        <v>-4.001</v>
-      </c>
-      <c r="V95" s="12" t="n">
-        <v>41.889</v>
-      </c>
-      <c r="W95" s="12" t="n">
-        <v>-9.282999999999999</v>
-      </c>
-      <c r="X95" s="12" t="n">
-        <v>-18.27</v>
+      <c r="A95" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용</t>
+        </is>
+      </c>
+      <c r="C95" s="22" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="22" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="W95" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
+          <t>주식교부비</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0.153</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="G96" s="22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="22" t="n">
         <v>0</v>
       </c>
       <c r="J96" s="22" t="n">
@@ -6476,10 +6536,10 @@
         <v>0</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="X96" s="22" t="n">
         <v>0</v>
@@ -6488,1016 +6548,1153 @@
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>특별이익 합계</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>5.338</v>
+        <v>-0.111</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>0.094</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>0</v>
+        <v>0.396</v>
       </c>
       <c r="G97" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="H97" s="22" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>0.777</v>
+      </c>
       <c r="J97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K97" s="22" t="n">
-        <v>0.617</v>
+        <v>0</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>1.063</v>
       </c>
       <c r="V97" s="22" t="n">
-        <v>5.338</v>
+        <v>-0.111</v>
       </c>
       <c r="W97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X97" s="22" t="n">
-        <v>0.617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n">
+        <v>15.815</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>13.254</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>42.187</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <v>54.383</v>
+      </c>
+      <c r="G98" s="22" t="n">
+        <v>29.092</v>
+      </c>
+      <c r="H98" s="22" t="n">
+        <v>50.915</v>
+      </c>
+      <c r="I98" s="22" t="n">
+        <v>40.482</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>45.743</v>
       </c>
       <c r="K98" s="22" t="n">
-        <v>30.75</v>
+        <v>85.53100000000001</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>95.849</v>
+      </c>
+      <c r="N98" s="22" t="n">
+        <v>121.531</v>
+      </c>
+      <c r="V98" s="22" t="n">
+        <v>15.815</v>
+      </c>
+      <c r="W98" s="22" t="n">
+        <v>29.092</v>
       </c>
       <c r="X98" s="22" t="n">
-        <v>30.75</v>
+        <v>85.53100000000001</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="C99" s="22" t="n">
-        <v>3.898</v>
-      </c>
-      <c r="F99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V99" s="22" t="n">
-        <v>3.898</v>
-      </c>
-      <c r="W99" s="22" t="n">
-        <v>0</v>
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>41.889</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>247.296</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>400.647</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>-8.725</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>-9.282999999999999</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>186.718</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>506.189</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>152.402</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>-18.27</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>837.732</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>37.077</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>-4.001</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>41.889</v>
+      </c>
+      <c r="W99" s="12" t="n">
+        <v>-9.282999999999999</v>
+      </c>
+      <c r="X99" s="12" t="n">
+        <v>-18.27</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>50.757</v>
-      </c>
-      <c r="F100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>87.858</v>
-      </c>
-      <c r="K100" s="22" t="n">
-        <v>30.75</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>50.757</v>
-      </c>
-      <c r="W100" s="22" t="n">
-        <v>87.858</v>
-      </c>
-      <c r="X100" s="22" t="n">
-        <v>30.75</v>
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G100" s="17">
+        <f>IF(OR(G99="",C99=""),"",IF(C99&lt;=0,"",IFERROR(G99/C99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H100" s="17">
+        <f>IF(OR(H99="",D99=""),"",IF(D99&lt;=0,"",IFERROR(H99/D99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="17">
+        <f>IF(OR(I99="",E99=""),"",IF(E99&lt;=0,"",IFERROR(I99/E99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="17">
+        <f>IF(OR(J99="",F99=""),"",IF(F99&lt;=0,"",IFERROR(J99/F99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF(OR(K99="",G99=""),"",IF(G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L100" s="17">
+        <f>IF(OR(L99="",H99=""),"",IF(H99&lt;=0,"",IFERROR(L99/H99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M100" s="17">
+        <f>IF(OR(M99="",I99=""),"",IF(I99&lt;=0,"",IFERROR(M99/I99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N100" s="17">
+        <f>IF(OR(N99="",J99=""),"",IF(J99&lt;=0,"",IFERROR(N99/J99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V100" s="17">
+        <f>IF(OR(V99="",U99=""),"",IF(U99&lt;=0,"",IFERROR(V99/U99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W100" s="17">
+        <f>IF(OR(W99="",V99=""),"",IF(V99&lt;=0,"",IFERROR(W99/V99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X100" s="17">
+        <f>IF(OR(X99="",W99=""),"",IF(W99&lt;=0,"",IFERROR(X99/W99-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>247.296</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>410.147</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>-8.725</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>-97.14100000000001</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>186.718</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>506.189</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>152.402</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>-48.403</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>837.732</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>37.077</v>
-      </c>
-      <c r="N101" s="12" t="n">
-        <v>-24.739</v>
-      </c>
-      <c r="V101" s="12" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="W101" s="12" t="n">
-        <v>-97.14100000000001</v>
-      </c>
-      <c r="X101" s="12" t="n">
-        <v>-48.403</v>
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>보상금 수취</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>특별이익 합계</t>
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>9.763</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>63.778</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>140.107</v>
+        <v>5.338</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>-0.879</v>
+        <v>0</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>12.432</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>47.052</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>157.656</v>
+        <v>0</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>34.658</v>
+        <v>0</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>5.364</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>248.161</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>32.695</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>-6.329</v>
+        <v>0.617</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>9.763</v>
+        <v>5.338</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>12.432</v>
+        <v>0</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>5.364</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="n">
-        <v>-24.922</v>
-      </c>
-      <c r="D103" s="22" t="n">
-        <v>13.876</v>
-      </c>
-      <c r="E103" s="22" t="n">
-        <v>-4.392</v>
-      </c>
-      <c r="F103" s="22" t="n">
-        <v>-7.241</v>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>-46.472</v>
-      </c>
-      <c r="H103" s="22" t="n">
-        <v>14.837</v>
-      </c>
-      <c r="I103" s="22" t="n">
-        <v>-4.048</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>16.231</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="K103" s="22" t="n">
-        <v>-34.065</v>
-      </c>
-      <c r="L103" s="22" t="n">
-        <v>13.308</v>
-      </c>
-      <c r="M103" s="22" t="n">
-        <v>-13.328</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>7.612</v>
-      </c>
-      <c r="V103" s="22" t="n">
-        <v>-24.922</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>-46.472</v>
+        <v>30.75</v>
       </c>
       <c r="X103" s="22" t="n">
-        <v>-34.065</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="n">
+        <v>3.898</v>
+      </c>
+      <c r="F104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="22" t="n">
+        <v>3.898</v>
+      </c>
+      <c r="W104" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>50.757</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>87.858</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>50.757</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>87.858</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>247.296</v>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>410.147</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>-8.725</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>-97.14100000000001</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>186.718</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>506.189</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>152.402</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>-48.403</v>
+      </c>
+      <c r="L106" s="12" t="n">
+        <v>837.732</v>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>37.077</v>
+      </c>
+      <c r="N106" s="12" t="n">
+        <v>-24.739</v>
+      </c>
+      <c r="V106" s="12" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="W106" s="12" t="n">
+        <v>-97.14100000000001</v>
+      </c>
+      <c r="X106" s="12" t="n">
+        <v>-48.403</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>9.763</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>63.778</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>140.107</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>-0.879</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>12.432</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>47.052</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>157.656</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>34.658</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>5.364</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>248.161</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>32.695</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>-6.329</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>9.763</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>12.432</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>5.364</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="n">
+        <v>-24.922</v>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>13.876</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>-4.392</v>
+      </c>
+      <c r="F108" s="22" t="n">
+        <v>-7.241</v>
+      </c>
+      <c r="G108" s="22" t="n">
+        <v>-46.472</v>
+      </c>
+      <c r="H108" s="22" t="n">
+        <v>14.837</v>
+      </c>
+      <c r="I108" s="22" t="n">
+        <v>-4.048</v>
+      </c>
+      <c r="J108" s="22" t="n">
+        <v>16.231</v>
+      </c>
+      <c r="K108" s="22" t="n">
+        <v>-34.065</v>
+      </c>
+      <c r="L108" s="22" t="n">
+        <v>13.308</v>
+      </c>
+      <c r="M108" s="22" t="n">
+        <v>-13.328</v>
+      </c>
+      <c r="N108" s="22" t="n">
+        <v>7.612</v>
+      </c>
+      <c r="V108" s="22" t="n">
+        <v>-24.922</v>
+      </c>
+      <c r="W108" s="22" t="n">
+        <v>-46.472</v>
+      </c>
+      <c r="X108" s="22" t="n">
+        <v>-34.065</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
+        <is>
           <t>법인세 등 합계</t>
         </is>
       </c>
-      <c r="C104" s="22" t="n">
+      <c r="C109" s="22" t="n">
         <v>-15.159</v>
       </c>
-      <c r="D104" s="22" t="n">
+      <c r="D109" s="22" t="n">
         <v>77.654</v>
       </c>
-      <c r="E104" s="22" t="n">
+      <c r="E109" s="22" t="n">
         <v>135.715</v>
       </c>
-      <c r="F104" s="22" t="n">
+      <c r="F109" s="22" t="n">
         <v>-8.119999999999999</v>
       </c>
-      <c r="G104" s="22" t="n">
+      <c r="G109" s="22" t="n">
         <v>-34.041</v>
       </c>
-      <c r="H104" s="22" t="n">
+      <c r="H109" s="22" t="n">
         <v>61.89</v>
       </c>
-      <c r="I104" s="22" t="n">
+      <c r="I109" s="22" t="n">
         <v>153.608</v>
       </c>
-      <c r="J104" s="22" t="n">
+      <c r="J109" s="22" t="n">
         <v>50.889</v>
       </c>
-      <c r="K104" s="22" t="n">
+      <c r="K109" s="22" t="n">
         <v>-28.702</v>
       </c>
-      <c r="L104" s="22" t="n">
+      <c r="L109" s="22" t="n">
         <v>261.47</v>
       </c>
-      <c r="M104" s="22" t="n">
+      <c r="M109" s="22" t="n">
         <v>19.365</v>
       </c>
-      <c r="N104" s="22" t="n">
+      <c r="N109" s="22" t="n">
         <v>1.284</v>
       </c>
-      <c r="V104" s="22" t="n">
+      <c r="V109" s="22" t="n">
         <v>-15.159</v>
       </c>
-      <c r="W104" s="22" t="n">
+      <c r="W109" s="22" t="n">
         <v>-34.041</v>
       </c>
-      <c r="X104" s="22" t="n">
+      <c r="X109" s="22" t="n">
         <v>-28.702</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C105" s="12" t="n">
+      <c r="C110" s="12" t="n">
         <v>11.629</v>
       </c>
-      <c r="D105" s="12" t="n">
+      <c r="D110" s="12" t="n">
         <v>169.642</v>
       </c>
-      <c r="E105" s="12" t="n">
+      <c r="E110" s="12" t="n">
         <v>274.431</v>
       </c>
-      <c r="F105" s="12" t="n">
+      <c r="F110" s="12" t="n">
         <v>-0.604</v>
       </c>
-      <c r="G105" s="12" t="n">
+      <c r="G110" s="12" t="n">
         <v>-63.101</v>
       </c>
-      <c r="H105" s="12" t="n">
+      <c r="H110" s="12" t="n">
         <v>124.827</v>
       </c>
-      <c r="I105" s="12" t="n">
+      <c r="I110" s="12" t="n">
         <v>352.581</v>
       </c>
-      <c r="J105" s="12" t="n">
+      <c r="J110" s="12" t="n">
         <v>101.514</v>
       </c>
-      <c r="K105" s="12" t="n">
+      <c r="K110" s="12" t="n">
         <v>-19.702</v>
       </c>
-      <c r="L105" s="12" t="n">
+      <c r="L110" s="12" t="n">
         <v>576.261</v>
       </c>
-      <c r="M105" s="12" t="n">
+      <c r="M110" s="12" t="n">
         <v>17.712</v>
       </c>
-      <c r="N105" s="12" t="n">
+      <c r="N110" s="12" t="n">
         <v>-26.023</v>
       </c>
-      <c r="V105" s="12" t="n">
+      <c r="V110" s="12" t="n">
         <v>11.629</v>
       </c>
-      <c r="W105" s="12" t="n">
+      <c r="W110" s="12" t="n">
         <v>-63.101</v>
       </c>
-      <c r="X105" s="12" t="n">
+      <c r="X110" s="12" t="n">
         <v>-19.702</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="18" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G111" s="17">
+        <f>IF(OR(G110="",C110=""),"",IF(C110&lt;=0,"",IFERROR(G110/C110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H111" s="17">
+        <f>IF(OR(H110="",D110=""),"",IF(D110&lt;=0,"",IFERROR(H110/D110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I111" s="17">
+        <f>IF(OR(I110="",E110=""),"",IF(E110&lt;=0,"",IFERROR(I110/E110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J111" s="17">
+        <f>IF(OR(J110="",F110=""),"",IF(F110&lt;=0,"",IFERROR(J110/F110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF(OR(K110="",G110=""),"",IF(G110&lt;=0,"",IFERROR(K110/G110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L111" s="17">
+        <f>IF(OR(L110="",H110=""),"",IF(H110&lt;=0,"",IFERROR(L110/H110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M111" s="17">
+        <f>IF(OR(M110="",I110=""),"",IF(I110&lt;=0,"",IFERROR(M110/I110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N111" s="17">
+        <f>IF(OR(N110="",J110=""),"",IF(J110&lt;=0,"",IFERROR(N110/J110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V111" s="17">
+        <f>IF(OR(V110="",U110=""),"",IF(U110&lt;=0,"",IFERROR(V110/U110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W111" s="17">
+        <f>IF(OR(W110="",V110=""),"",IF(V110&lt;=0,"",IFERROR(W110/V110-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X111" s="17">
+        <f>IF(OR(X110="",W110=""),"",IF(W110&lt;=0,"",IFERROR(X110/W110-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B107" s="44" t="inlineStr">
+      <c r="B113" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-      <c r="J107" s="18" t="n"/>
-      <c r="K107" s="18" t="n"/>
-      <c r="L107" s="18" t="n"/>
-      <c r="M107" s="18" t="n"/>
-      <c r="N107" s="18" t="n"/>
-      <c r="O107" s="18" t="n"/>
-      <c r="P107" s="18" t="n"/>
-      <c r="Q107" s="18" t="n"/>
-      <c r="R107" s="18" t="n"/>
-      <c r="S107" s="18" t="n"/>
-      <c r="T107" s="18" t="n"/>
-      <c r="U107" s="18" t="n"/>
-      <c r="V107" s="18" t="n"/>
-      <c r="W107" s="18" t="n"/>
-      <c r="X107" s="18" t="n"/>
-      <c r="Y107" s="18" t="n"/>
-      <c r="Z107" s="18" t="n"/>
-      <c r="AA107" s="18" t="n"/>
-      <c r="AB107" s="18" t="n"/>
-      <c r="AC107" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+      <c r="J113" s="18" t="n"/>
+      <c r="K113" s="18" t="n"/>
+      <c r="L113" s="18" t="n"/>
+      <c r="M113" s="18" t="n"/>
+      <c r="N113" s="18" t="n"/>
+      <c r="O113" s="18" t="n"/>
+      <c r="P113" s="18" t="n"/>
+      <c r="Q113" s="18" t="n"/>
+      <c r="R113" s="18" t="n"/>
+      <c r="S113" s="18" t="n"/>
+      <c r="T113" s="18" t="n"/>
+      <c r="U113" s="18" t="n"/>
+      <c r="V113" s="18" t="n"/>
+      <c r="W113" s="18" t="n"/>
+      <c r="X113" s="18" t="n"/>
+      <c r="Y113" s="18" t="n"/>
+      <c r="Z113" s="18" t="n"/>
+      <c r="AA113" s="18" t="n"/>
+      <c r="AB113" s="18" t="n"/>
+      <c r="AC113" s="18" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>2023.4Q</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>2024.1Q</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="H114" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="I108" s="5" t="inlineStr">
+      <c r="I114" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="J108" s="5" t="inlineStr">
+      <c r="J114" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="K108" s="5" t="inlineStr">
+      <c r="K114" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="L114" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="M108" s="5" t="inlineStr">
+      <c r="M114" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="N108" s="5" t="inlineStr">
+      <c r="N114" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="O108" s="5" t="inlineStr">
+      <c r="O114" s="5" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="P108" s="5" t="inlineStr">
+      <c r="P114" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="Q108" s="5" t="inlineStr">
+      <c r="Q114" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="R108" s="5" t="inlineStr">
+      <c r="R114" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="S108" s="5" t="inlineStr">
+      <c r="S114" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="T108" s="5" t="inlineStr">
+      <c r="T114" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="U108" s="5" t="inlineStr">
+      <c r="U114" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V108" s="5" t="inlineStr">
+      <c r="V114" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="W108" s="5" t="inlineStr">
+      <c r="W114" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="X108" s="5" t="inlineStr">
+      <c r="X114" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="Y108" s="5" t="inlineStr">
+      <c r="Y114" s="5" t="inlineStr">
         <is>
           <t>2026(MW)</t>
         </is>
       </c>
-      <c r="Z108" s="5" t="inlineStr">
+      <c r="Z114" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="AA108" s="5" t="inlineStr">
+      <c r="AA114" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AB108" s="5" t="inlineStr">
+      <c r="AB114" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AC108" s="5" t="inlineStr">
+      <c r="AC114" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C109" s="12" t="n">
+      <c r="C115" s="12" t="n">
         <v>425.872</v>
       </c>
-      <c r="E109" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>657.443</v>
       </c>
-      <c r="G109" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>551.577</v>
       </c>
-      <c r="I109" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>692.907</v>
       </c>
-      <c r="K109" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>796.9059999999999</v>
       </c>
-      <c r="M109" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>874.809</v>
       </c>
-      <c r="U109" s="12" t="n">
+      <c r="U115" s="12" t="n">
         <v>40.18</v>
       </c>
-      <c r="V109" s="12" t="n">
+      <c r="V115" s="12" t="n">
         <v>425.872</v>
       </c>
-      <c r="W109" s="12" t="n">
+      <c r="W115" s="12" t="n">
         <v>551.577</v>
       </c>
-      <c r="X109" s="12" t="n">
+      <c r="X115" s="12" t="n">
         <v>796.9059999999999</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C110" s="22" t="n">
-        <v>367.464</v>
-      </c>
-      <c r="E110" s="22" t="n">
-        <v>175.772</v>
-      </c>
-      <c r="G110" s="22" t="n">
-        <v>369.555</v>
-      </c>
-      <c r="I110" s="22" t="n">
-        <v>198.185</v>
-      </c>
-      <c r="K110" s="22" t="n">
-        <v>398.754</v>
-      </c>
-      <c r="M110" s="22" t="n">
-        <v>212.714</v>
-      </c>
-      <c r="U110" s="22" t="n">
-        <v>372.773</v>
-      </c>
-      <c r="V110" s="22" t="n">
-        <v>367.464</v>
-      </c>
-      <c r="W110" s="22" t="n">
-        <v>369.555</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>398.754</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>46.858</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>87.858</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>30.75</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>329.526</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>46.858</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>87.858</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>30.75</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="G112" s="22" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="K112" s="22" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>-0.196</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>0.198</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>수주손실 충당금 증감</t>
-        </is>
-      </c>
-      <c r="C114" s="22" t="n">
-        <v>15.132</v>
-      </c>
-      <c r="E114" s="22" t="n">
-        <v>-12.922</v>
-      </c>
-      <c r="G114" s="22" t="n">
-        <v>-13.004</v>
-      </c>
-      <c r="I114" s="22" t="n">
-        <v>-1.552</v>
-      </c>
-      <c r="K114" s="22" t="n">
-        <v>-2.319</v>
-      </c>
-      <c r="M114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" s="22" t="n">
-        <v>-3.494</v>
-      </c>
-      <c r="V114" s="22" t="n">
-        <v>15.132</v>
-      </c>
-      <c r="W114" s="22" t="n">
-        <v>-13.004</v>
-      </c>
-      <c r="X114" s="22" t="n">
-        <v>-2.319</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>손해보상손실 충당금 증감액</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>-6.133</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>-32</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>-6.133</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>-32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>고정자산 수증이익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C116" s="22" t="n">
-        <v>0</v>
+        <v>367.464</v>
+      </c>
+      <c r="E116" s="22" t="n">
+        <v>175.772</v>
+      </c>
+      <c r="G116" s="22" t="n">
+        <v>369.555</v>
+      </c>
+      <c r="I116" s="22" t="n">
+        <v>198.185</v>
+      </c>
+      <c r="K116" s="22" t="n">
+        <v>398.754</v>
+      </c>
+      <c r="M116" s="22" t="n">
+        <v>212.714</v>
       </c>
       <c r="U116" s="22" t="n">
-        <v>-0.497</v>
+        <v>372.773</v>
       </c>
       <c r="V116" s="22" t="n">
-        <v>0</v>
+        <v>367.464</v>
+      </c>
+      <c r="W116" s="22" t="n">
+        <v>369.555</v>
+      </c>
+      <c r="X116" s="22" t="n">
+        <v>398.754</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C117" s="22" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="E117" s="22" t="n">
-        <v>-0.08599999999999999</v>
+        <v>46.858</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>-0.876</v>
-      </c>
-      <c r="I117" s="22" t="n">
-        <v>-1.494</v>
+        <v>87.858</v>
       </c>
       <c r="K117" s="22" t="n">
-        <v>-4.331</v>
-      </c>
-      <c r="M117" s="22" t="n">
-        <v>-2.257</v>
+        <v>30.75</v>
       </c>
       <c r="U117" s="22" t="n">
-        <v>-0.007</v>
+        <v>329.526</v>
       </c>
       <c r="V117" s="22" t="n">
-        <v>-0.008</v>
+        <v>46.858</v>
       </c>
       <c r="W117" s="22" t="n">
-        <v>-0.876</v>
+        <v>87.858</v>
       </c>
       <c r="X117" s="22" t="n">
-        <v>-4.331</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="C118" s="22" t="n">
-        <v>-1.32</v>
+        <v>-0.196</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>0</v>
+        <v>0.193</v>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="M118" s="22" t="n">
+        <v>-0.034</v>
       </c>
       <c r="U118" s="22" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="V118" s="22" t="n">
-        <v>-1.32</v>
+        <v>-0.196</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>0</v>
+        <v>0.193</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>0.198</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>협찬금 수입</t>
+          <t>임원 상여충당금 증감</t>
         </is>
       </c>
       <c r="C119" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E119" s="22" t="n">
-        <v>-0.297</v>
+        <v>-9</v>
       </c>
       <c r="G119" s="22" t="n">
-        <v>-1.177</v>
+        <v>0</v>
       </c>
       <c r="I119" s="22" t="n">
-        <v>0</v>
+        <v>-6.9</v>
       </c>
       <c r="K119" s="22" t="n">
-        <v>-0.209</v>
+        <v>-4.8</v>
       </c>
       <c r="M119" s="22" t="n">
-        <v>-0.21</v>
+        <v>-2.1</v>
       </c>
       <c r="U119" s="22" t="n">
-        <v>-0.556</v>
+        <v>0.9</v>
       </c>
       <c r="V119" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W119" s="22" t="n">
-        <v>-1.177</v>
+        <v>0</v>
       </c>
       <c r="X119" s="22" t="n">
-        <v>-0.209</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
+          <t>수주손실 충당금 증감</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
-        <v>-5.338</v>
+        <v>15.132</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>-12.922</v>
       </c>
       <c r="G120" s="22" t="n">
+        <v>-13.004</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>-1.552</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <v>-2.319</v>
+      </c>
+      <c r="M120" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>0</v>
+        <v>-3.494</v>
       </c>
       <c r="V120" s="22" t="n">
-        <v>-5.338</v>
+        <v>15.132</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>0</v>
+        <v>-13.004</v>
+      </c>
+      <c r="X120" s="22" t="n">
+        <v>-2.319</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>위약금</t>
+          <t>손해보상손실 충당금 증감액</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
-        <v>0.011</v>
+        <v>-6.133</v>
+      </c>
+      <c r="E121" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="I121" s="22" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K121" s="22" t="n">
+        <v>-32</v>
+      </c>
+      <c r="M121" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>1.141</v>
+        <v>6.133</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>0.011</v>
+        <v>-6.133</v>
+      </c>
+      <c r="W121" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="X121" s="22" t="n">
+        <v>-32</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>고정자산 수증이익</t>
         </is>
       </c>
       <c r="C122" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="22" t="n">
-        <v>26.469</v>
-      </c>
-      <c r="G122" s="22" t="n">
-        <v>55.369</v>
-      </c>
-      <c r="I122" s="22" t="n">
-        <v>16.481</v>
-      </c>
-      <c r="K122" s="22" t="n">
-        <v>52.333</v>
-      </c>
-      <c r="M122" s="22" t="n">
-        <v>36.474</v>
-      </c>
       <c r="U122" s="22" t="n">
-        <v>9.039999999999999</v>
+        <v>-0.497</v>
       </c>
       <c r="V122" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="W122" s="22" t="n">
-        <v>55.369</v>
-      </c>
-      <c r="X122" s="22" t="n">
-        <v>52.333</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C123" s="22" t="n">
-        <v>7.249</v>
+        <v>-0.008</v>
       </c>
       <c r="E123" s="22" t="n">
-        <v>0</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>0</v>
+        <v>-0.876</v>
+      </c>
+      <c r="I123" s="22" t="n">
+        <v>-1.494</v>
+      </c>
+      <c r="K123" s="22" t="n">
+        <v>-4.331</v>
+      </c>
+      <c r="M123" s="22" t="n">
+        <v>-2.257</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>12.251</v>
+        <v>-0.007</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>7.249</v>
+        <v>-0.008</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>0</v>
+        <v>-0.876</v>
+      </c>
+      <c r="X123" s="22" t="n">
+        <v>-4.331</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C124" s="22" t="n">
-        <v>8.212</v>
+        <v>-1.32</v>
       </c>
       <c r="E124" s="22" t="n">
         <v>0</v>
@@ -7509,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>8.212</v>
+        <v>-1.32</v>
       </c>
       <c r="W124" s="22" t="n">
         <v>0</v>
@@ -7518,48 +7715,48 @@
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>주식교부비</t>
+          <t>협찬금 수입</t>
         </is>
       </c>
       <c r="C125" s="22" t="n">
-        <v>10.207</v>
+        <v>0</v>
       </c>
       <c r="E125" s="22" t="n">
-        <v>0.323</v>
+        <v>-0.297</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>0.473</v>
+        <v>-1.177</v>
       </c>
       <c r="I125" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>0</v>
+        <v>-0.209</v>
+      </c>
+      <c r="M125" s="22" t="n">
+        <v>-0.21</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>0</v>
+        <v>-0.556</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>10.207</v>
+        <v>0</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>0.473</v>
+        <v>-1.177</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>0</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>손해보상 손실</t>
+          <t>신주예약권 환입이익</t>
         </is>
       </c>
       <c r="C126" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E126" s="22" t="n">
-        <v>0</v>
+        <v>-5.338</v>
       </c>
       <c r="G126" s="22" t="n">
         <v>0</v>
@@ -7568,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>10</v>
+        <v>-5.338</v>
       </c>
       <c r="W126" s="22" t="n">
         <v>0</v>
@@ -7577,1710 +7774,1680 @@
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>주식보상비용</t>
+          <t>위약금</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="22" t="n">
-        <v>10.208</v>
-      </c>
-      <c r="G127" s="22" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="I127" s="22" t="n">
-        <v>29.706</v>
-      </c>
-      <c r="K127" s="22" t="n">
-        <v>63.309</v>
-      </c>
-      <c r="M127" s="22" t="n">
-        <v>63.496</v>
+        <v>0.011</v>
+      </c>
+      <c r="U127" s="22" t="n">
+        <v>1.141</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>31.34</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>63.309</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
+          <t>지급수수료</t>
         </is>
       </c>
       <c r="C128" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E128" s="22" t="n">
-        <v>-9.5</v>
+        <v>26.469</v>
       </c>
       <c r="G128" s="22" t="n">
-        <v>-9.5</v>
+        <v>55.369</v>
       </c>
       <c r="I128" s="22" t="n">
-        <v>0</v>
+        <v>16.481</v>
       </c>
       <c r="K128" s="22" t="n">
-        <v>-1.171</v>
+        <v>52.333</v>
+      </c>
+      <c r="M128" s="22" t="n">
+        <v>36.474</v>
+      </c>
+      <c r="U128" s="22" t="n">
+        <v>9.039999999999999</v>
       </c>
       <c r="V128" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>-9.5</v>
+        <v>55.369</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>-1.171</v>
+        <v>52.333</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>이자비용·사채이자</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="C129" s="22" t="n">
-        <v>48.777</v>
+        <v>7.249</v>
       </c>
       <c r="E129" s="22" t="n">
-        <v>26.183</v>
+        <v>0</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>68.923</v>
-      </c>
-      <c r="I129" s="22" t="n">
-        <v>70.33499999999999</v>
-      </c>
-      <c r="K129" s="22" t="n">
-        <v>162.961</v>
-      </c>
-      <c r="M129" s="22" t="n">
-        <v>127.61</v>
+        <v>0</v>
       </c>
       <c r="U129" s="22" t="n">
-        <v>32.919</v>
+        <v>12.251</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>48.777</v>
+        <v>7.249</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>68.923</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>162.961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>상장 관련 비용</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-178.229</v>
+        <v>8.212</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>2.209</v>
+        <v>0</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>-20.979</v>
-      </c>
-      <c r="I130" s="22" t="n">
-        <v>-56.304</v>
-      </c>
-      <c r="K130" s="22" t="n">
-        <v>-10.071</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>-26.043</v>
+        <v>0</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-69.97</v>
+        <v>0</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-178.229</v>
+        <v>8.212</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-20.979</v>
-      </c>
-      <c r="X130" s="22" t="n">
-        <v>-10.071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>계약자산 증감액</t>
+          <t>주식교부비</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
-        <v>-17.346</v>
+        <v>10.207</v>
       </c>
       <c r="E131" s="22" t="n">
-        <v>16.474</v>
+        <v>0.323</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>13.203</v>
+        <v>0.473</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>1.164</v>
+        <v>0</v>
       </c>
       <c r="K131" s="22" t="n">
-        <v>4.587</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>-97.369</v>
+        <v>0</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-3.289</v>
+        <v>0</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>-17.346</v>
+        <v>10.207</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>13.203</v>
+        <v>0.473</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>4.587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>미성공사 지출금 증감액</t>
+          <t>손해보상 손실</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
-        <v>-0.001</v>
+        <v>10</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-0.119</v>
+        <v>0</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="I132" s="22" t="n">
-        <v>-0.759</v>
-      </c>
-      <c r="K132" s="22" t="n">
-        <v>-0.08500000000000001</v>
-      </c>
-      <c r="M132" s="22" t="n">
-        <v>-0.113</v>
+        <v>0</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>12.826</v>
+        <v>0</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>-0.001</v>
+        <v>10</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="X132" s="22" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>미성업무 지출금 증감액</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
-        <v>-3.263</v>
+        <v>0</v>
       </c>
       <c r="E133" s="22" t="n">
-        <v>1.888</v>
+        <v>10.208</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>3.263</v>
+        <v>31.34</v>
       </c>
       <c r="I133" s="22" t="n">
-        <v>-0.575</v>
+        <v>29.706</v>
       </c>
       <c r="K133" s="22" t="n">
-        <v>0</v>
+        <v>63.309</v>
       </c>
       <c r="M133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>12.051</v>
+        <v>63.496</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>-3.263</v>
+        <v>0</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>3.263</v>
+        <v>31.34</v>
       </c>
       <c r="X133" s="22" t="n">
-        <v>0</v>
+        <v>63.309</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>판매용 부동산 증감액</t>
+          <t>보상금 수취</t>
         </is>
       </c>
       <c r="C134" s="22" t="n">
-        <v>458.368</v>
+        <v>0</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-1360.403</v>
+        <v>-9.5</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>-2308.269</v>
+        <v>-9.5</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>2374.402</v>
+        <v>0</v>
       </c>
       <c r="K134" s="22" t="n">
-        <v>1975.98</v>
-      </c>
-      <c r="M134" s="22" t="n">
-        <v>1038.441</v>
-      </c>
-      <c r="U134" s="22" t="n">
-        <v>-589.914</v>
+        <v>-1.171</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>458.368</v>
+        <v>0</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>-2308.269</v>
+        <v>-9.5</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>1975.98</v>
+        <v>-1.171</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>이자비용·사채이자</t>
         </is>
       </c>
       <c r="C135" s="22" t="n">
-        <v>45.917</v>
+        <v>48.777</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>7.708</v>
+        <v>26.183</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>33.649</v>
+        <v>68.923</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>22.472</v>
+        <v>70.33499999999999</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>20.6</v>
+        <v>162.961</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>-25.837</v>
+        <v>127.61</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>20.248</v>
+        <v>32.919</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>45.917</v>
+        <v>48.777</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>33.649</v>
+        <v>68.923</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>20.6</v>
+        <v>162.961</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손익</t>
-        </is>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="n">
+        <v>-178.229</v>
+      </c>
+      <c r="E136" s="22" t="n">
+        <v>2.209</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>0</v>
+        <v>-20.979</v>
+      </c>
+      <c r="I136" s="22" t="n">
+        <v>-56.304</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>-0.617</v>
+        <v>-10.071</v>
+      </c>
+      <c r="M136" s="22" t="n">
+        <v>-26.043</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>-69.97</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>-178.229</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>0</v>
+        <v>-20.979</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>-0.617</v>
+        <v>-10.071</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>선급비용 증감</t>
+          <t>계약자산 증감액</t>
         </is>
       </c>
       <c r="C137" s="22" t="n">
-        <v>-29.366</v>
+        <v>-17.346</v>
       </c>
       <c r="E137" s="22" t="n">
-        <v>-12.012</v>
+        <v>16.474</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>-37.125</v>
+        <v>13.203</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>5.775</v>
+        <v>1.164</v>
       </c>
       <c r="K137" s="22" t="n">
-        <v>11.402</v>
+        <v>4.587</v>
       </c>
       <c r="M137" s="22" t="n">
-        <v>-17.133</v>
+        <v>-97.369</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>-29.051</v>
+        <v>-3.289</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>-29.366</v>
+        <v>-17.346</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>-37.125</v>
+        <v>13.203</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>11.402</v>
+        <v>4.587</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>장기선급비용 증감</t>
+          <t>미성공사 지출금 증감액</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>0.255</v>
+        <v>-0.001</v>
+      </c>
+      <c r="E138" s="22" t="n">
+        <v>-0.119</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>0</v>
+        <v>0.143</v>
+      </c>
+      <c r="I138" s="22" t="n">
+        <v>-0.759</v>
+      </c>
+      <c r="K138" s="22" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="M138" s="22" t="n">
+        <v>-0.113</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>3.06</v>
+        <v>12.826</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>0.255</v>
+        <v>-0.001</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>0</v>
+        <v>0.143</v>
+      </c>
+      <c r="X138" s="22" t="n">
+        <v>-0.08500000000000001</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
+          <t>미성업무 지출금 증감액</t>
         </is>
       </c>
       <c r="C139" s="22" t="n">
-        <v>8.253</v>
+        <v>-3.263</v>
       </c>
       <c r="E139" s="22" t="n">
-        <v>-167.771</v>
+        <v>1.888</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>3.373</v>
+        <v>3.263</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>-7.551</v>
+        <v>-0.575</v>
       </c>
       <c r="K139" s="22" t="n">
-        <v>-5.638</v>
+        <v>0</v>
       </c>
       <c r="M139" s="22" t="n">
-        <v>37.366</v>
+        <v>0</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>54.026</v>
+        <v>12.051</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>8.253</v>
+        <v>-3.263</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>3.373</v>
+        <v>3.263</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-5.638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>판매용 부동산 증감액</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>-47.061</v>
+        <v>458.368</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>5.911</v>
+        <v>-1360.403</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>14.71</v>
+        <v>-2308.269</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>32.933</v>
+        <v>2374.402</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>97.709</v>
+        <v>1975.98</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>-50.927</v>
+        <v>1038.441</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>26.431</v>
+        <v>-589.914</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>-47.061</v>
+        <v>458.368</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>14.71</v>
+        <v>-2308.269</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>97.709</v>
+        <v>1975.98</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>미지급비용 증감</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="C141" s="22" t="n">
-        <v>22.299</v>
+        <v>45.917</v>
       </c>
       <c r="E141" s="22" t="n">
-        <v>-4.702</v>
+        <v>7.708</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>-0.482</v>
+        <v>33.649</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>-7.26</v>
+        <v>22.472</v>
       </c>
       <c r="K141" s="22" t="n">
-        <v>18.96</v>
+        <v>20.6</v>
       </c>
       <c r="M141" s="22" t="n">
-        <v>-9.377000000000001</v>
+        <v>-25.837</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>16.329</v>
+        <v>20.248</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>22.299</v>
+        <v>45.917</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>-0.482</v>
+        <v>33.649</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>18.96</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>선수금 증감</t>
-        </is>
-      </c>
-      <c r="C142" s="22" t="n">
-        <v>12.077</v>
-      </c>
-      <c r="E142" s="22" t="n">
-        <v>22.774</v>
+          <t>고정자산 매각손익</t>
+        </is>
       </c>
       <c r="G142" s="22" t="n">
-        <v>99.64100000000001</v>
-      </c>
-      <c r="I142" s="22" t="n">
-        <v>-32.008</v>
+        <v>0</v>
       </c>
       <c r="K142" s="22" t="n">
-        <v>-13.338</v>
-      </c>
-      <c r="M142" s="22" t="n">
-        <v>-32.046</v>
-      </c>
-      <c r="U142" s="22" t="n">
-        <v>12.908</v>
-      </c>
-      <c r="V142" s="22" t="n">
-        <v>12.077</v>
+        <v>-0.617</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>99.64100000000001</v>
+        <v>0</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-13.338</v>
+        <v>-0.617</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>선급비용 증감</t>
         </is>
       </c>
       <c r="C143" s="22" t="n">
-        <v>286.535</v>
+        <v>-29.366</v>
       </c>
       <c r="E143" s="22" t="n">
-        <v>-275.301</v>
+        <v>-12.012</v>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>-37.125</v>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>5.775</v>
+      </c>
+      <c r="K143" s="22" t="n">
+        <v>11.402</v>
+      </c>
+      <c r="M143" s="22" t="n">
+        <v>-17.133</v>
       </c>
       <c r="U143" s="22" t="n">
-        <v>27.762</v>
+        <v>-29.051</v>
       </c>
       <c r="V143" s="22" t="n">
-        <v>286.535</v>
+        <v>-29.366</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>-37.125</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>11.402</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>장기선급비용 증감</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>286.535</v>
-      </c>
-      <c r="E144" s="22" t="n">
-        <v>-275.301</v>
+        <v>0.255</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>-273.019</v>
-      </c>
-      <c r="I144" s="22" t="n">
-        <v>79.431</v>
-      </c>
-      <c r="K144" s="22" t="n">
-        <v>269.494</v>
-      </c>
-      <c r="M144" s="22" t="n">
-        <v>-272.881</v>
+        <v>0</v>
+      </c>
+      <c r="U144" s="22" t="n">
+        <v>3.06</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>286.535</v>
+        <v>0.255</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-273.019</v>
-      </c>
-      <c r="X144" s="22" t="n">
-        <v>269.494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>예수금 증감</t>
+          <t>기타 자산 증감</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>1.67</v>
+        <v>8.253</v>
       </c>
       <c r="E145" s="22" t="n">
-        <v>34.561</v>
+        <v>-167.771</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>3.785</v>
+        <v>3.373</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>29.874</v>
+        <v>-7.551</v>
       </c>
       <c r="K145" s="22" t="n">
-        <v>27.209</v>
+        <v>-5.638</v>
       </c>
       <c r="M145" s="22" t="n">
-        <v>24.378</v>
+        <v>37.366</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>53.787</v>
+        <v>54.026</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>1.67</v>
+        <v>8.253</v>
       </c>
       <c r="W145" s="22" t="n">
-        <v>3.785</v>
+        <v>3.373</v>
       </c>
       <c r="X145" s="22" t="n">
-        <v>27.209</v>
+        <v>-5.638</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>예수보증금 증감액</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
-        <v>112.962</v>
+        <v>-47.061</v>
       </c>
       <c r="E146" s="22" t="n">
-        <v>35.098</v>
+        <v>5.911</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>101.628</v>
+        <v>14.71</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>28.595</v>
+        <v>32.933</v>
       </c>
       <c r="K146" s="22" t="n">
-        <v>-36.276</v>
+        <v>97.709</v>
       </c>
       <c r="M146" s="22" t="n">
-        <v>98.77</v>
+        <v>-50.927</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>215.822</v>
+        <v>26.431</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>112.962</v>
+        <v>-47.061</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>101.628</v>
+        <v>14.71</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-36.276</v>
+        <v>97.709</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
+          <t>미지급비용 증감</t>
         </is>
       </c>
       <c r="C147" s="22" t="n">
-        <v>117.824</v>
+        <v>22.299</v>
       </c>
       <c r="E147" s="22" t="n">
-        <v>76.48999999999999</v>
+        <v>-4.702</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>35.132</v>
+        <v>-0.482</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>93.90900000000001</v>
+        <v>-7.26</v>
       </c>
       <c r="K147" s="22" t="n">
-        <v>161.062</v>
+        <v>18.96</v>
       </c>
       <c r="M147" s="22" t="n">
-        <v>-46.889</v>
+        <v>-9.377000000000001</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>-46.211</v>
+        <v>16.329</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>117.824</v>
+        <v>22.299</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>35.132</v>
+        <v>-0.482</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>161.062</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>선수금 증감</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>0.011</v>
+        <v>12.077</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>0.23</v>
+        <v>22.774</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>0.23</v>
+        <v>99.64100000000001</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>0.058</v>
+        <v>-32.008</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>0.058</v>
+        <v>-13.338</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>0</v>
+        <v>-32.046</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>0.189</v>
+        <v>12.908</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>0.011</v>
+        <v>12.077</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>0.23</v>
+        <v>99.64100000000001</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>0.058</v>
+        <v>-13.338</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C149" s="22" t="n">
-        <v>1717.685</v>
+        <v>286.535</v>
       </c>
       <c r="E149" s="22" t="n">
-        <v>-751.978</v>
-      </c>
-      <c r="G149" s="22" t="n">
-        <v>-1148.382</v>
-      </c>
-      <c r="I149" s="22" t="n">
-        <v>3531.845</v>
-      </c>
-      <c r="K149" s="22" t="n">
-        <v>3981.418</v>
-      </c>
-      <c r="M149" s="22" t="n">
-        <v>1930.84</v>
+        <v>-275.301</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>517.5170000000001</v>
+        <v>27.762</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>1717.685</v>
-      </c>
-      <c r="W149" s="22" t="n">
-        <v>-1148.382</v>
-      </c>
-      <c r="X149" s="22" t="n">
-        <v>3981.418</v>
+        <v>286.535</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="C150" s="22" t="n">
-        <v>-45.229</v>
+        <v>286.535</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-25.563</v>
+        <v>-275.301</v>
       </c>
       <c r="G150" s="22" t="n">
-        <v>-73.98999999999999</v>
+        <v>-273.019</v>
       </c>
       <c r="I150" s="22" t="n">
-        <v>-71.508</v>
+        <v>79.431</v>
       </c>
       <c r="K150" s="22" t="n">
-        <v>-164.696</v>
+        <v>269.494</v>
       </c>
       <c r="M150" s="22" t="n">
-        <v>-133.549</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>-33.948</v>
+        <v>-272.881</v>
       </c>
       <c r="V150" s="22" t="n">
-        <v>-45.229</v>
+        <v>286.535</v>
       </c>
       <c r="W150" s="22" t="n">
-        <v>-73.98999999999999</v>
+        <v>-273.019</v>
       </c>
       <c r="X150" s="22" t="n">
-        <v>-164.696</v>
+        <v>269.494</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>예수금 증감</t>
         </is>
       </c>
       <c r="C151" s="22" t="n">
-        <v>0.008</v>
+        <v>1.67</v>
       </c>
       <c r="E151" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>34.561</v>
       </c>
       <c r="G151" s="22" t="n">
-        <v>0.122</v>
+        <v>3.785</v>
       </c>
       <c r="I151" s="22" t="n">
-        <v>0.861</v>
+        <v>29.874</v>
       </c>
       <c r="K151" s="22" t="n">
-        <v>2.981</v>
+        <v>27.209</v>
       </c>
       <c r="M151" s="22" t="n">
-        <v>1.528</v>
+        <v>24.378</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>0.007</v>
+        <v>53.787</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>0.008</v>
+        <v>1.67</v>
       </c>
       <c r="W151" s="22" t="n">
-        <v>0.122</v>
+        <v>3.785</v>
       </c>
       <c r="X151" s="22" t="n">
-        <v>2.981</v>
+        <v>27.209</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
+          <t>예수보증금 증감액</t>
         </is>
       </c>
       <c r="C152" s="22" t="n">
-        <v>1.32</v>
+        <v>112.962</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>0</v>
+        <v>35.098</v>
       </c>
       <c r="G152" s="22" t="n">
-        <v>0</v>
+        <v>101.628</v>
+      </c>
+      <c r="I152" s="22" t="n">
+        <v>28.595</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>-36.276</v>
+      </c>
+      <c r="M152" s="22" t="n">
+        <v>98.77</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>0</v>
+        <v>215.822</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>1.32</v>
+        <v>112.962</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>0</v>
+        <v>101.628</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>-36.276</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>기타 부채 증감</t>
         </is>
       </c>
       <c r="C153" s="22" t="n">
-        <v>-157.871</v>
+        <v>117.824</v>
       </c>
       <c r="E153" s="22" t="n">
-        <v>-58.438</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="G153" s="22" t="n">
-        <v>-121.019</v>
+        <v>35.132</v>
       </c>
       <c r="I153" s="22" t="n">
-        <v>-152.563</v>
+        <v>93.90900000000001</v>
       </c>
       <c r="K153" s="22" t="n">
-        <v>-260.402</v>
+        <v>161.062</v>
       </c>
       <c r="M153" s="22" t="n">
-        <v>-137.155</v>
+        <v>-46.889</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>-72.386</v>
+        <v>-46.211</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>-157.871</v>
+        <v>117.824</v>
       </c>
       <c r="W153" s="22" t="n">
-        <v>-121.019</v>
+        <v>35.132</v>
       </c>
       <c r="X153" s="22" t="n">
-        <v>-260.402</v>
+        <v>161.062</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>보상금 수취</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C154" s="22" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="E154" s="22" t="n">
-        <v>9.5</v>
+        <v>0.23</v>
       </c>
       <c r="G154" s="22" t="n">
-        <v>9.5</v>
+        <v>0.23</v>
       </c>
       <c r="I154" s="22" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="K154" s="22" t="n">
-        <v>1.171</v>
+        <v>0.058</v>
+      </c>
+      <c r="M154" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" s="22" t="n">
+        <v>0.189</v>
       </c>
       <c r="V154" s="22" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="W154" s="22" t="n">
-        <v>9.5</v>
+        <v>0.23</v>
       </c>
       <c r="X154" s="22" t="n">
-        <v>1.171</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>보상금 지급액</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C155" s="22" t="n">
-        <v>-10</v>
+        <v>1717.685</v>
       </c>
       <c r="E155" s="22" t="n">
-        <v>0</v>
+        <v>-751.978</v>
       </c>
       <c r="G155" s="22" t="n">
-        <v>0</v>
+        <v>-1148.382</v>
+      </c>
+      <c r="I155" s="22" t="n">
+        <v>3531.845</v>
+      </c>
+      <c r="K155" s="22" t="n">
+        <v>3981.418</v>
+      </c>
+      <c r="M155" s="22" t="n">
+        <v>1930.84</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>0</v>
+        <v>517.5170000000001</v>
       </c>
       <c r="V155" s="22" t="n">
-        <v>-10</v>
+        <v>1717.685</v>
       </c>
       <c r="W155" s="22" t="n">
-        <v>0</v>
+        <v>-1148.382</v>
+      </c>
+      <c r="X155" s="22" t="n">
+        <v>3981.418</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>협찬금 수취액</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="C156" s="22" t="n">
-        <v>0</v>
+        <v>-45.229</v>
       </c>
       <c r="E156" s="22" t="n">
-        <v>0.297</v>
+        <v>-25.563</v>
       </c>
       <c r="G156" s="22" t="n">
-        <v>1.177</v>
+        <v>-73.98999999999999</v>
       </c>
       <c r="I156" s="22" t="n">
-        <v>0</v>
+        <v>-71.508</v>
       </c>
       <c r="K156" s="22" t="n">
-        <v>0.209</v>
+        <v>-164.696</v>
       </c>
       <c r="M156" s="22" t="n">
-        <v>0.21</v>
+        <v>-133.549</v>
       </c>
       <c r="U156" s="22" t="n">
-        <v>0.556</v>
+        <v>-33.948</v>
       </c>
       <c r="V156" s="22" t="n">
-        <v>0</v>
+        <v>-45.229</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>1.177</v>
+        <v>-73.98999999999999</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>0.209</v>
+        <v>-164.696</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>위약금 지급액</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
-        <v>-0.011</v>
+        <v>0.008</v>
+      </c>
+      <c r="E157" s="22" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G157" s="22" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="I157" s="22" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="K157" s="22" t="n">
+        <v>2.981</v>
+      </c>
+      <c r="M157" s="22" t="n">
+        <v>1.528</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>-1.141</v>
+        <v>0.007</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>-0.011</v>
+        <v>0.008</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="X157" s="22" t="n">
+        <v>2.981</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보조금 수취</t>
         </is>
       </c>
       <c r="C158" s="22" t="n">
-        <v>-0.011</v>
+        <v>1.32</v>
       </c>
       <c r="E158" s="22" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="G158" s="22" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="I158" s="22" t="n">
-        <v>-0.058</v>
-      </c>
-      <c r="K158" s="22" t="n">
-        <v>-0.058</v>
-      </c>
-      <c r="M158" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>-0.011</v>
+        <v>1.32</v>
       </c>
       <c r="W158" s="22" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="X158" s="22" t="n">
-        <v>-0.058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="n">
-        <v>1505.901</v>
-      </c>
-      <c r="E159" s="12" t="n">
-        <v>-826.404</v>
-      </c>
-      <c r="G159" s="12" t="n">
-        <v>-1332.824</v>
-      </c>
-      <c r="I159" s="12" t="n">
-        <v>3308.576</v>
-      </c>
-      <c r="K159" s="12" t="n">
-        <v>3560.622</v>
-      </c>
-      <c r="M159" s="12" t="n">
-        <v>1661.873</v>
-      </c>
-      <c r="U159" s="12" t="n">
-        <v>410.604</v>
-      </c>
-      <c r="V159" s="12" t="n">
-        <v>1505.901</v>
-      </c>
-      <c r="W159" s="12" t="n">
-        <v>-1332.824</v>
-      </c>
-      <c r="X159" s="12" t="n">
-        <v>3560.622</v>
+      <c r="A159" s="20" t="inlineStr">
+        <is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="C159" s="22" t="n">
+        <v>-157.871</v>
+      </c>
+      <c r="E159" s="22" t="n">
+        <v>-58.438</v>
+      </c>
+      <c r="G159" s="22" t="n">
+        <v>-121.019</v>
+      </c>
+      <c r="I159" s="22" t="n">
+        <v>-152.563</v>
+      </c>
+      <c r="K159" s="22" t="n">
+        <v>-260.402</v>
+      </c>
+      <c r="M159" s="22" t="n">
+        <v>-137.155</v>
+      </c>
+      <c r="U159" s="22" t="n">
+        <v>-72.386</v>
+      </c>
+      <c r="V159" s="22" t="n">
+        <v>-157.871</v>
+      </c>
+      <c r="W159" s="22" t="n">
+        <v>-121.019</v>
+      </c>
+      <c r="X159" s="22" t="n">
+        <v>-260.402</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
+          <t>보상금 수취</t>
         </is>
       </c>
       <c r="C160" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="U160" s="22" t="n">
-        <v>10</v>
+      <c r="E160" s="22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G160" s="22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I160" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="22" t="n">
+        <v>1.171</v>
       </c>
       <c r="V160" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="W160" s="22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="X160" s="22" t="n">
+        <v>1.171</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>보상금 지급액</t>
         </is>
       </c>
       <c r="C161" s="22" t="n">
-        <v>-2911.956</v>
+        <v>-10</v>
       </c>
       <c r="E161" s="22" t="n">
-        <v>-115.996</v>
+        <v>0</v>
       </c>
       <c r="G161" s="22" t="n">
-        <v>-3197.148</v>
-      </c>
-      <c r="I161" s="22" t="n">
-        <v>-4143.581</v>
-      </c>
-      <c r="K161" s="22" t="n">
-        <v>-7739.481</v>
-      </c>
-      <c r="M161" s="22" t="n">
-        <v>-5356.227</v>
+        <v>0</v>
       </c>
       <c r="U161" s="22" t="n">
-        <v>-2255.84</v>
+        <v>0</v>
       </c>
       <c r="V161" s="22" t="n">
-        <v>-2911.956</v>
+        <v>-10</v>
       </c>
       <c r="W161" s="22" t="n">
-        <v>-3197.148</v>
-      </c>
-      <c r="X161" s="22" t="n">
-        <v>-7739.481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>유형자산 제각 지출</t>
+          <t>협찬금 수취액</t>
         </is>
       </c>
       <c r="C162" s="22" t="n">
-        <v>-1.178</v>
+        <v>0</v>
       </c>
       <c r="E162" s="22" t="n">
-        <v>0</v>
+        <v>0.297</v>
       </c>
       <c r="G162" s="22" t="n">
-        <v>0</v>
+        <v>1.177</v>
+      </c>
+      <c r="I162" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="22" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="M162" s="22" t="n">
+        <v>0.21</v>
       </c>
       <c r="U162" s="22" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="V162" s="22" t="n">
-        <v>-1.178</v>
+        <v>0</v>
       </c>
       <c r="W162" s="22" t="n">
-        <v>0</v>
+        <v>1.177</v>
+      </c>
+      <c r="X162" s="22" t="n">
+        <v>0.209</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
-      </c>
-      <c r="G163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" s="22" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="W163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" s="22" t="n">
-        <v>0.617</v>
+          <t>위약금 지급액</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="U163" s="22" t="n">
+        <v>-1.141</v>
+      </c>
+      <c r="V163" s="22" t="n">
+        <v>-0.011</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C164" s="22" t="n">
-        <v>-17.242</v>
+        <v>-0.011</v>
       </c>
       <c r="E164" s="22" t="n">
-        <v>-7.942</v>
+        <v>-0.23</v>
       </c>
       <c r="G164" s="22" t="n">
-        <v>-7.942</v>
+        <v>-0.23</v>
       </c>
       <c r="I164" s="22" t="n">
-        <v>-17.336</v>
+        <v>-0.058</v>
       </c>
       <c r="K164" s="22" t="n">
-        <v>-27.291</v>
+        <v>-0.058</v>
       </c>
       <c r="M164" s="22" t="n">
-        <v>-1.727</v>
-      </c>
-      <c r="U164" s="22" t="n">
-        <v>-58.394</v>
+        <v>0</v>
       </c>
       <c r="V164" s="22" t="n">
-        <v>-17.242</v>
+        <v>-0.011</v>
       </c>
       <c r="W164" s="22" t="n">
-        <v>-7.942</v>
+        <v>-0.23</v>
       </c>
       <c r="X164" s="22" t="n">
-        <v>-27.291</v>
+        <v>-0.058</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="20" t="inlineStr">
-        <is>
-          <t>자산복구부채 이행 지출</t>
-        </is>
-      </c>
-      <c r="C165" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" s="22" t="n">
-        <v>-5.951</v>
-      </c>
-      <c r="V165" s="22" t="n">
-        <v>0</v>
+      <c r="A165" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="n">
+        <v>1505.901</v>
+      </c>
+      <c r="E165" s="12" t="n">
+        <v>-826.404</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>-1332.824</v>
+      </c>
+      <c r="I165" s="12" t="n">
+        <v>3308.576</v>
+      </c>
+      <c r="K165" s="12" t="n">
+        <v>3560.622</v>
+      </c>
+      <c r="M165" s="12" t="n">
+        <v>1661.873</v>
+      </c>
+      <c r="U165" s="12" t="n">
+        <v>410.604</v>
+      </c>
+      <c r="V165" s="12" t="n">
+        <v>1505.901</v>
+      </c>
+      <c r="W165" s="12" t="n">
+        <v>-1332.824</v>
+      </c>
+      <c r="X165" s="12" t="n">
+        <v>3560.622</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>장기대여</t>
+          <t>정기예금 인출</t>
         </is>
       </c>
       <c r="C166" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E166" s="22" t="n">
-        <v>-33.423</v>
-      </c>
-      <c r="G166" s="22" t="n">
-        <v>-59.91</v>
-      </c>
-      <c r="I166" s="22" t="n">
-        <v>-10.105</v>
-      </c>
-      <c r="K166" s="22" t="n">
-        <v>-17.423</v>
-      </c>
-      <c r="M166" s="22" t="n">
-        <v>0</v>
+      <c r="U166" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="V166" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="W166" s="22" t="n">
-        <v>-59.91</v>
-      </c>
-      <c r="X166" s="22" t="n">
-        <v>-17.423</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>장기대여금 회수</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C167" s="22" t="n">
-        <v>0</v>
+        <v>-2911.956</v>
       </c>
       <c r="E167" s="22" t="n">
-        <v>0.202</v>
+        <v>-115.996</v>
       </c>
       <c r="G167" s="22" t="n">
-        <v>2.541</v>
+        <v>-3197.148</v>
       </c>
       <c r="I167" s="22" t="n">
-        <v>2.339</v>
+        <v>-4143.581</v>
       </c>
       <c r="K167" s="22" t="n">
-        <v>5.085</v>
+        <v>-7739.481</v>
       </c>
       <c r="M167" s="22" t="n">
-        <v>3.057</v>
+        <v>-5356.227</v>
+      </c>
+      <c r="U167" s="22" t="n">
+        <v>-2255.84</v>
       </c>
       <c r="V167" s="22" t="n">
-        <v>0</v>
+        <v>-2911.956</v>
       </c>
       <c r="W167" s="22" t="n">
-        <v>2.541</v>
+        <v>-3197.148</v>
       </c>
       <c r="X167" s="22" t="n">
-        <v>5.085</v>
+        <v>-7739.481</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
+          <t>유형자산 제각 지출</t>
         </is>
       </c>
       <c r="C168" s="22" t="n">
-        <v>-105.056</v>
+        <v>-1.178</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-73.625</v>
+        <v>0</v>
       </c>
       <c r="G168" s="22" t="n">
-        <v>-108.717</v>
-      </c>
-      <c r="I168" s="22" t="n">
-        <v>-10.909</v>
-      </c>
-      <c r="K168" s="22" t="n">
-        <v>-23.531</v>
-      </c>
-      <c r="M168" s="22" t="n">
-        <v>-106.754</v>
+        <v>0</v>
       </c>
       <c r="U168" s="22" t="n">
-        <v>-200.256</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>-105.056</v>
+        <v>-1.178</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>-108.717</v>
-      </c>
-      <c r="X168" s="22" t="n">
-        <v>-23.531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
-        </is>
-      </c>
-      <c r="C169" s="22" t="n">
-        <v>56.756</v>
-      </c>
-      <c r="E169" s="22" t="n">
-        <v>28.167</v>
+          <t>유형자산 매각</t>
+        </is>
       </c>
       <c r="G169" s="22" t="n">
-        <v>48.966</v>
-      </c>
-      <c r="I169" s="22" t="n">
-        <v>41.186</v>
+        <v>0</v>
       </c>
       <c r="K169" s="22" t="n">
-        <v>61.87</v>
-      </c>
-      <c r="M169" s="22" t="n">
-        <v>61.02</v>
-      </c>
-      <c r="U169" s="22" t="n">
-        <v>31.955</v>
-      </c>
-      <c r="V169" s="22" t="n">
-        <v>56.756</v>
+        <v>0.617</v>
       </c>
       <c r="W169" s="22" t="n">
-        <v>48.966</v>
+        <v>0</v>
       </c>
       <c r="X169" s="22" t="n">
-        <v>61.87</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>출자금 납입</t>
-        </is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="C170" s="22" t="n">
+        <v>-17.242</v>
+      </c>
+      <c r="E170" s="22" t="n">
+        <v>-7.942</v>
+      </c>
+      <c r="G170" s="22" t="n">
+        <v>-7.942</v>
       </c>
       <c r="I170" s="22" t="n">
-        <v>0</v>
+        <v>-17.336</v>
+      </c>
+      <c r="K170" s="22" t="n">
+        <v>-27.291</v>
       </c>
       <c r="M170" s="22" t="n">
-        <v>-10</v>
+        <v>-1.727</v>
+      </c>
+      <c r="U170" s="22" t="n">
+        <v>-58.394</v>
+      </c>
+      <c r="V170" s="22" t="n">
+        <v>-17.242</v>
+      </c>
+      <c r="W170" s="22" t="n">
+        <v>-7.942</v>
+      </c>
+      <c r="X170" s="22" t="n">
+        <v>-27.291</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="20" t="inlineStr">
         <is>
-          <t>투자 및 기타자산 증감액</t>
+          <t>자산복구부채 이행 지출</t>
         </is>
       </c>
       <c r="C171" s="22" t="n">
-        <v>-72.36</v>
-      </c>
-      <c r="E171" s="22" t="n">
-        <v>-44.805</v>
-      </c>
-      <c r="G171" s="22" t="n">
-        <v>-60.192</v>
-      </c>
-      <c r="I171" s="22" t="n">
-        <v>-97.57599999999999</v>
-      </c>
-      <c r="K171" s="22" t="n">
-        <v>-186.117</v>
-      </c>
-      <c r="M171" s="22" t="n">
-        <v>-137.353</v>
+        <v>0</v>
       </c>
       <c r="U171" s="22" t="n">
-        <v>-50.175</v>
+        <v>-5.951</v>
       </c>
       <c r="V171" s="22" t="n">
-        <v>-72.36</v>
-      </c>
-      <c r="W171" s="22" t="n">
-        <v>-60.192</v>
-      </c>
-      <c r="X171" s="22" t="n">
-        <v>-186.117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C172" s="12" t="n">
-        <v>-3051.036</v>
-      </c>
-      <c r="E172" s="12" t="n">
-        <v>-247.424</v>
-      </c>
-      <c r="G172" s="12" t="n">
-        <v>-3382.402</v>
-      </c>
-      <c r="I172" s="12" t="n">
-        <v>-4235.981</v>
-      </c>
-      <c r="K172" s="12" t="n">
-        <v>-7926.27</v>
-      </c>
-      <c r="M172" s="12" t="n">
-        <v>-5547.984</v>
-      </c>
-      <c r="U172" s="12" t="n">
-        <v>-2528.67</v>
-      </c>
-      <c r="V172" s="12" t="n">
-        <v>-3051.036</v>
-      </c>
-      <c r="W172" s="12" t="n">
-        <v>-3382.402</v>
-      </c>
-      <c r="X172" s="12" t="n">
-        <v>-7926.27</v>
+      <c r="A172" s="20" t="inlineStr">
+        <is>
+          <t>장기대여</t>
+        </is>
+      </c>
+      <c r="C172" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" s="22" t="n">
+        <v>-33.423</v>
+      </c>
+      <c r="G172" s="22" t="n">
+        <v>-59.91</v>
+      </c>
+      <c r="I172" s="22" t="n">
+        <v>-10.105</v>
+      </c>
+      <c r="K172" s="22" t="n">
+        <v>-17.423</v>
+      </c>
+      <c r="M172" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" s="22" t="n">
+        <v>-59.91</v>
+      </c>
+      <c r="X172" s="22" t="n">
+        <v>-17.423</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 순증감</t>
+          <t>장기대여금 회수</t>
         </is>
       </c>
       <c r="C173" s="22" t="n">
-        <v>1842</v>
+        <v>0</v>
       </c>
       <c r="E173" s="22" t="n">
-        <v>-1727</v>
+        <v>0.202</v>
       </c>
       <c r="G173" s="22" t="n">
-        <v>-1842</v>
+        <v>2.541</v>
       </c>
       <c r="I173" s="22" t="n">
-        <v>135</v>
+        <v>2.339</v>
       </c>
       <c r="K173" s="22" t="n">
-        <v>0</v>
+        <v>5.085</v>
       </c>
       <c r="M173" s="22" t="n">
-        <v>1490</v>
-      </c>
-      <c r="U173" s="22" t="n">
-        <v>-157</v>
+        <v>3.057</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>1842</v>
+        <v>0</v>
       </c>
       <c r="W173" s="22" t="n">
-        <v>-1842</v>
+        <v>2.541</v>
       </c>
       <c r="X173" s="22" t="n">
-        <v>0</v>
+        <v>5.085</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>임차보증금·보증금 납입</t>
         </is>
       </c>
       <c r="C174" s="22" t="n">
-        <v>922.042</v>
+        <v>-105.056</v>
       </c>
       <c r="E174" s="22" t="n">
-        <v>3299</v>
+        <v>-73.625</v>
       </c>
       <c r="G174" s="22" t="n">
-        <v>7333</v>
+        <v>-108.717</v>
       </c>
       <c r="I174" s="22" t="n">
-        <v>3520</v>
+        <v>-10.909</v>
       </c>
       <c r="K174" s="22" t="n">
-        <v>9890</v>
+        <v>-23.531</v>
       </c>
       <c r="M174" s="22" t="n">
-        <v>3638.54</v>
+        <v>-106.754</v>
       </c>
       <c r="U174" s="22" t="n">
-        <v>3181</v>
+        <v>-200.256</v>
       </c>
       <c r="V174" s="22" t="n">
-        <v>922.042</v>
+        <v>-105.056</v>
       </c>
       <c r="W174" s="22" t="n">
-        <v>7333</v>
+        <v>-108.717</v>
       </c>
       <c r="X174" s="22" t="n">
-        <v>9890</v>
+        <v>-23.531</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>임차보증금·보증금 회수</t>
         </is>
       </c>
       <c r="C175" s="22" t="n">
-        <v>-1132.054</v>
+        <v>56.756</v>
       </c>
       <c r="E175" s="22" t="n">
-        <v>-1132.991</v>
+        <v>28.167</v>
       </c>
       <c r="G175" s="22" t="n">
-        <v>-1557.67</v>
+        <v>48.966</v>
       </c>
       <c r="I175" s="22" t="n">
-        <v>-1704.294</v>
+        <v>41.186</v>
       </c>
       <c r="K175" s="22" t="n">
-        <v>-5661.186</v>
+        <v>61.87</v>
       </c>
       <c r="M175" s="22" t="n">
-        <v>-1612.596</v>
+        <v>61.02</v>
       </c>
       <c r="U175" s="22" t="n">
-        <v>-623.515</v>
+        <v>31.955</v>
       </c>
       <c r="V175" s="22" t="n">
-        <v>-1132.054</v>
+        <v>56.756</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>-1557.67</v>
+        <v>48.966</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>-5661.186</v>
+        <v>61.87</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>사채 상환</t>
-        </is>
-      </c>
-      <c r="C176" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="E176" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U176" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="V176" s="22" t="n">
-        <v>-20</v>
-      </c>
-      <c r="W176" s="22" t="n">
-        <v>0</v>
+          <t>출자금 납입</t>
+        </is>
+      </c>
+      <c r="I176" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="22" t="n">
+        <v>-10</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 행사에 따른 주식 발행</t>
+          <t>투자 및 기타자산 증감액</t>
         </is>
       </c>
       <c r="C177" s="22" t="n">
-        <v>2.521</v>
+        <v>-72.36</v>
       </c>
       <c r="E177" s="22" t="n">
-        <v>0.711</v>
+        <v>-44.805</v>
       </c>
       <c r="G177" s="22" t="n">
-        <v>3.649</v>
+        <v>-60.192</v>
       </c>
       <c r="I177" s="22" t="n">
-        <v>2.796</v>
+        <v>-97.57599999999999</v>
       </c>
       <c r="K177" s="22" t="n">
-        <v>6.348</v>
+        <v>-186.117</v>
       </c>
       <c r="M177" s="22" t="n">
-        <v>11.284</v>
+        <v>-137.353</v>
       </c>
       <c r="U177" s="22" t="n">
-        <v>0</v>
+        <v>-50.175</v>
       </c>
       <c r="V177" s="22" t="n">
-        <v>2.521</v>
+        <v>-72.36</v>
       </c>
       <c r="W177" s="22" t="n">
-        <v>3.649</v>
+        <v>-60.192</v>
       </c>
       <c r="X177" s="22" t="n">
-        <v>6.348</v>
+        <v>-186.117</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="20" t="inlineStr">
-        <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="C178" s="22" t="n">
-        <v>1268.859</v>
-      </c>
-      <c r="G178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U178" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V178" s="22" t="n">
-        <v>1268.859</v>
-      </c>
-      <c r="W178" s="22" t="n">
-        <v>0</v>
+      <c r="A178" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="n">
+        <v>-3051.036</v>
+      </c>
+      <c r="E178" s="12" t="n">
+        <v>-247.424</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>-3382.402</v>
+      </c>
+      <c r="I178" s="12" t="n">
+        <v>-4235.981</v>
+      </c>
+      <c r="K178" s="12" t="n">
+        <v>-7926.27</v>
+      </c>
+      <c r="M178" s="12" t="n">
+        <v>-5547.984</v>
+      </c>
+      <c r="U178" s="12" t="n">
+        <v>-2528.67</v>
+      </c>
+      <c r="V178" s="12" t="n">
+        <v>-3051.036</v>
+      </c>
+      <c r="W178" s="12" t="n">
+        <v>-3382.402</v>
+      </c>
+      <c r="X178" s="12" t="n">
+        <v>-7926.27</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>주식 발행 지출</t>
+          <t>단기차입금 순증감</t>
         </is>
       </c>
       <c r="C179" s="22" t="n">
-        <v>-10.207</v>
+        <v>1842</v>
       </c>
       <c r="E179" s="22" t="n">
-        <v>-0.323</v>
+        <v>-1727</v>
       </c>
       <c r="G179" s="22" t="n">
-        <v>-0.473</v>
+        <v>-1842</v>
       </c>
       <c r="I179" s="22" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="K179" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="M179" s="22" t="n">
+        <v>1490</v>
+      </c>
       <c r="U179" s="22" t="n">
-        <v>0</v>
+        <v>-157</v>
       </c>
       <c r="V179" s="22" t="n">
-        <v>-10.207</v>
+        <v>1842</v>
       </c>
       <c r="W179" s="22" t="n">
-        <v>-0.473</v>
+        <v>-1842</v>
       </c>
       <c r="X179" s="22" t="n">
         <v>0</v>
@@ -9289,258 +9456,450 @@
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>신주청약증거금 납입 수입</t>
-        </is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="C180" s="22" t="n">
+        <v>922.042</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>0</v>
+        <v>3299</v>
+      </c>
+      <c r="G180" s="22" t="n">
+        <v>7333</v>
       </c>
       <c r="I180" s="22" t="n">
-        <v>0.047</v>
+        <v>3520</v>
+      </c>
+      <c r="K180" s="22" t="n">
+        <v>9890</v>
       </c>
       <c r="M180" s="22" t="n">
-        <v>0</v>
+        <v>3638.54</v>
+      </c>
+      <c r="U180" s="22" t="n">
+        <v>3181</v>
+      </c>
+      <c r="V180" s="22" t="n">
+        <v>922.042</v>
+      </c>
+      <c r="W180" s="22" t="n">
+        <v>7333</v>
+      </c>
+      <c r="X180" s="22" t="n">
+        <v>9890</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>장기차입금 상환</t>
         </is>
       </c>
       <c r="C181" s="22" t="n">
-        <v>0</v>
+        <v>-1132.054</v>
       </c>
       <c r="E181" s="22" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-1132.991</v>
       </c>
       <c r="G181" s="22" t="n">
-        <v>-0.218</v>
+        <v>-1557.67</v>
       </c>
       <c r="I181" s="22" t="n">
-        <v>0</v>
+        <v>-1704.294</v>
       </c>
       <c r="K181" s="22" t="n">
-        <v>0</v>
+        <v>-5661.186</v>
       </c>
       <c r="M181" s="22" t="n">
-        <v>-0.136</v>
+        <v>-1612.596</v>
+      </c>
+      <c r="U181" s="22" t="n">
+        <v>-623.515</v>
       </c>
       <c r="V181" s="22" t="n">
-        <v>0</v>
+        <v>-1132.054</v>
       </c>
       <c r="W181" s="22" t="n">
-        <v>-0.218</v>
+        <v>-1557.67</v>
       </c>
       <c r="X181" s="22" t="n">
-        <v>0</v>
+        <v>-5661.186</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 발행</t>
+          <t>사채 상환</t>
         </is>
       </c>
       <c r="C182" s="22" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>1.908</v>
+        <v>0</v>
       </c>
       <c r="G182" s="22" t="n">
-        <v>1.908</v>
-      </c>
-      <c r="I182" s="22" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="K182" s="22" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="M182" s="22" t="n">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="U182" s="22" t="n">
-        <v>5.351</v>
+        <v>-20</v>
       </c>
       <c r="V182" s="22" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="W182" s="22" t="n">
-        <v>1.908</v>
-      </c>
-      <c r="X182" s="22" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
+          <t>신주예약권 행사에 따른 주식 발행</t>
         </is>
       </c>
       <c r="C183" s="22" t="n">
-        <v>-8.212</v>
+        <v>2.521</v>
+      </c>
+      <c r="E183" s="22" t="n">
+        <v>0.711</v>
       </c>
       <c r="G183" s="22" t="n">
-        <v>0</v>
+        <v>3.649</v>
+      </c>
+      <c r="I183" s="22" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="K183" s="22" t="n">
+        <v>6.348</v>
+      </c>
+      <c r="M183" s="22" t="n">
+        <v>11.284</v>
       </c>
       <c r="U183" s="22" t="n">
         <v>0</v>
       </c>
       <c r="V183" s="22" t="n">
-        <v>-8.212</v>
+        <v>2.521</v>
       </c>
       <c r="W183" s="22" t="n">
-        <v>0</v>
+        <v>3.649</v>
+      </c>
+      <c r="X183" s="22" t="n">
+        <v>6.348</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
-        </is>
-      </c>
-      <c r="E184" s="22" t="n">
-        <v>0</v>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="C184" s="22" t="n">
+        <v>1268.859</v>
       </c>
       <c r="G184" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I184" s="22" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="K184" s="22" t="n">
-        <v>-0.442</v>
-      </c>
-      <c r="M184" s="22" t="n">
-        <v>-0.331</v>
+      <c r="U184" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" s="22" t="n">
+        <v>1268.859</v>
       </c>
       <c r="W184" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="X184" s="22" t="n">
-        <v>-0.442</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>수수료 지급액</t>
+          <t>주식 발행 지출</t>
         </is>
       </c>
       <c r="C185" s="22" t="n">
-        <v>0</v>
+        <v>-10.207</v>
       </c>
       <c r="E185" s="22" t="n">
-        <v>-26.469</v>
+        <v>-0.323</v>
       </c>
       <c r="G185" s="22" t="n">
-        <v>-55.369</v>
+        <v>-0.473</v>
       </c>
       <c r="I185" s="22" t="n">
-        <v>-16.481</v>
+        <v>0</v>
       </c>
       <c r="K185" s="22" t="n">
-        <v>-52.333</v>
-      </c>
-      <c r="M185" s="22" t="n">
-        <v>-36.474</v>
+        <v>0</v>
       </c>
       <c r="U185" s="22" t="n">
-        <v>-9.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="V185" s="22" t="n">
-        <v>0</v>
+        <v>-10.207</v>
       </c>
       <c r="W185" s="22" t="n">
-        <v>-55.369</v>
+        <v>-0.473</v>
       </c>
       <c r="X185" s="22" t="n">
-        <v>-52.333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
+          <t>신주청약증거금 납입 수입</t>
         </is>
       </c>
       <c r="E186" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="I186" s="22" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="M186" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C187" s="12" t="n">
-        <v>2864.949</v>
-      </c>
-      <c r="E187" s="12" t="n">
-        <v>414.762</v>
-      </c>
-      <c r="G187" s="12" t="n">
-        <v>3882.825</v>
-      </c>
-      <c r="I187" s="12" t="n">
-        <v>1937.014</v>
-      </c>
-      <c r="K187" s="12" t="n">
-        <v>4182.443</v>
-      </c>
-      <c r="M187" s="12" t="n">
-        <v>3490.455</v>
-      </c>
-      <c r="U187" s="12" t="n">
-        <v>2376.795</v>
-      </c>
-      <c r="V187" s="12" t="n">
-        <v>2864.949</v>
-      </c>
-      <c r="W187" s="12" t="n">
-        <v>3882.825</v>
-      </c>
-      <c r="X187" s="12" t="n">
-        <v>4182.443</v>
+      <c r="A187" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" s="22" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="G187" s="22" t="n">
+        <v>-0.218</v>
+      </c>
+      <c r="I187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" s="22" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="V187" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" s="22" t="n">
+        <v>-0.218</v>
+      </c>
+      <c r="X187" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="20" t="inlineStr">
         <is>
+          <t>신주예약권 발행</t>
+        </is>
+      </c>
+      <c r="C188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" s="22" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="G188" s="22" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="I188" s="22" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="K188" s="22" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="M188" s="22" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="U188" s="22" t="n">
+        <v>5.351</v>
+      </c>
+      <c r="V188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" s="22" t="n">
+        <v>1.908</v>
+      </c>
+      <c r="X188" s="22" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="C189" s="22" t="n">
+        <v>-8.212</v>
+      </c>
+      <c r="G189" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" s="22" t="n">
+        <v>-8.212</v>
+      </c>
+      <c r="W189" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="E190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="K190" s="22" t="n">
+        <v>-0.442</v>
+      </c>
+      <c r="M190" s="22" t="n">
+        <v>-0.331</v>
+      </c>
+      <c r="W190" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X190" s="22" t="n">
+        <v>-0.442</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="20" t="inlineStr">
+        <is>
+          <t>수수료 지급액</t>
+        </is>
+      </c>
+      <c r="C191" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="22" t="n">
+        <v>-26.469</v>
+      </c>
+      <c r="G191" s="22" t="n">
+        <v>-55.369</v>
+      </c>
+      <c r="I191" s="22" t="n">
+        <v>-16.481</v>
+      </c>
+      <c r="K191" s="22" t="n">
+        <v>-52.333</v>
+      </c>
+      <c r="M191" s="22" t="n">
+        <v>-36.474</v>
+      </c>
+      <c r="U191" s="22" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>-55.369</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>-52.333</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="E192" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="n">
+        <v>2864.949</v>
+      </c>
+      <c r="E193" s="12" t="n">
+        <v>414.762</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>3882.825</v>
+      </c>
+      <c r="I193" s="12" t="n">
+        <v>1937.014</v>
+      </c>
+      <c r="K193" s="12" t="n">
+        <v>4182.443</v>
+      </c>
+      <c r="M193" s="12" t="n">
+        <v>3490.455</v>
+      </c>
+      <c r="U193" s="12" t="n">
+        <v>2376.795</v>
+      </c>
+      <c r="V193" s="12" t="n">
+        <v>2864.949</v>
+      </c>
+      <c r="W193" s="12" t="n">
+        <v>3882.825</v>
+      </c>
+      <c r="X193" s="12" t="n">
+        <v>4182.443</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="C188" s="22" t="n">
+      <c r="C194" s="22" t="n">
         <v>1319.814</v>
       </c>
-      <c r="E188" s="22" t="n">
+      <c r="E194" s="22" t="n">
         <v>-659.066</v>
       </c>
-      <c r="G188" s="22" t="n">
+      <c r="G194" s="22" t="n">
         <v>-832.401</v>
       </c>
-      <c r="I188" s="22" t="n">
+      <c r="I194" s="22" t="n">
         <v>1009.609</v>
       </c>
-      <c r="K188" s="22" t="n">
+      <c r="K194" s="22" t="n">
         <v>-183.205</v>
       </c>
-      <c r="M188" s="22" t="n">
+      <c r="M194" s="22" t="n">
         <v>-395.654</v>
       </c>
-      <c r="U188" s="22" t="n">
+      <c r="U194" s="22" t="n">
         <v>258.729</v>
       </c>
-      <c r="V188" s="22" t="n">
+      <c r="V194" s="22" t="n">
         <v>1319.814</v>
       </c>
-      <c r="W188" s="22" t="n">
+      <c r="W194" s="22" t="n">
         <v>-832.401</v>
       </c>
-      <c r="X188" s="22" t="n">
+      <c r="X194" s="22" t="n">
         <v>-183.205</v>
       </c>
     </row>
@@ -9580,7 +9939,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10869,7 +11228,7 @@
       <c r="K42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10917,7 +11276,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10965,7 +11324,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11013,7 +11372,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11061,7 +11420,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11109,7 +11468,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11157,7 +11516,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11167,39 +11526,39 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",H28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",I28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",J28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",K28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11222,7 +11581,7 @@
       <c r="K50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11270,7 +11629,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11318,7 +11677,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11366,7 +11725,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11414,7 +11773,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11462,7 +11821,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11527,7 +11886,7 @@
       <c r="K57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11575,7 +11934,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11585,45 +11944,45 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11633,45 +11992,45 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11681,45 +12040,45 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11729,39 +12088,39 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
@@ -11784,7 +12143,7 @@
       <c r="K63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11832,7 +12191,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11880,7 +12239,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11928,7 +12287,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14289,24 +14648,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
